--- a/afar_project/csv_path/excel_files/asset_register.xlsx
+++ b/afar_project/csv_path/excel_files/asset_register.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0002</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0003</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0004</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0006</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0007</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0008</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0009</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-17-0000</t>
+          <t>FRC-HQ-SLM-C-17-0010</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-17-0000</t>
+          <t>FRC-HQ-SLM-C-17-0011</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0012</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0013</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0014</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0015</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0016</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0017</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0018</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0019</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0020</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0021</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0022</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0023</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0024</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0025</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0027</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0028</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0029</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0030</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0031</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0032</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0033</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0034</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0035</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0036</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0037</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0038</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0039</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0040</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0041</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0042</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0043</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0044</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-17-0000</t>
+          <t>FRC-HQ-SLM-T-17-0045</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-17-0000</t>
+          <t>FRC-HQ-SLM-T-17-0046</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0047</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0048</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0049</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0050</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-17-0000</t>
+          <t>FRC-HQ-SLM-O-17-0051</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0052</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-17-0000</t>
+          <t>FRC-HQ-SLM-F-17-0053</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0054</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0055</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0056</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0057</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0058</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0059</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0060</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0061</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0000</t>
+          <t>FRC-HQ-SLM-O-18-0062</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0063</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0064</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0065</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0066</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0067</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0068</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0069</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0070</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0071</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0072</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0073</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0074</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0075</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-18-0000</t>
+          <t>FRC-HQ-SLM-T-18-0076</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0077</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0078</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0079</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0080</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0081</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0082</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0083</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0000</t>
+          <t>FRC-HQ-SLM-O-18-0084</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0085</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0086</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0000</t>
+          <t>FRC-HQ-SLM-O-18-0087</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0088</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0089</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-18-0000</t>
+          <t>FRC-HQ-SLM-C-18-0090</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0091</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0092</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0093</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0000</t>
+          <t>FRC-HQ-SLM-O-18-0094</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0000</t>
+          <t>FRC-HQ-SLM-F-18-0095</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0000</t>
+          <t>FRC-HQ-SLM-O-18-0096</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-18-0000</t>
+          <t>FRC-HQ-SLM-T-18-0097</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-18-0000</t>
+          <t>FRC-HQ-SLM-M-18-0098</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-18-0000</t>
+          <t>FRC-HQ-SLM-M-18-0099</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0100</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0101</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0102</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0103</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0104</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0105</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0106</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0107</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0108</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-18-0001</t>
+          <t>FRC-HQ-SLM-O-18-0109</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-18-0001</t>
+          <t>FRC-HQ-SLM-F-18-0110</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0111</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0112</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0113</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0114</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0115</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-19-0001</t>
+          <t>FRC-HQ-SLM-O-19-0116</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0117</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0118</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-19-0001</t>
+          <t>FRC-HQ-SLM-O-19-0119</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-19-0001</t>
+          <t>FRC-HQ-SLM-O-19-0120</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0121</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-19-0001</t>
+          <t>FRC-HQ-SLM-C-19-0122</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-19-0001</t>
+          <t>FRC-HQ-SLM-C-19-0123</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-19-0001</t>
+          <t>FRC-HQ-SLM-C-19-0124</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-19-0001</t>
+          <t>FRC-HQ-SLM-C-19-0125</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0126</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0127</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-19-0001</t>
+          <t>FRC-HQ-SLM-F-19-0128</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0129</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0130</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0131</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0132</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-20-0001</t>
+          <t>FRC-HQ-SLM-T-20-0133</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0134</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0135</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0136</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0137</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-20-0001</t>
+          <t>FRC-HQ-SLM-F-20-0138</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0139</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-20-0001</t>
+          <t>FRC-HQ-SLM-F-20-0140</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0141</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-20-0001</t>
+          <t>FRC-HQ-SLM-C-20-0142</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-21-0001</t>
+          <t>FRC-HQ-SLM-M-21-0143</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-21-0001</t>
+          <t>FRC-HQ-SLM-M-21-0144</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-21-0001</t>
+          <t>FRC-HQ-SLM-O-21-0145</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0146</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0147</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-21-0001</t>
+          <t>FRC-HQ-SLM-M-21-0148</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0001</t>
+          <t>FRC-HQ-SLM-F-21-0149</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-21-0001</t>
+          <t>FRC-HQ-SLM-O-21-0150</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0152</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0153</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0154</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0155</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0156</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0157</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -15056,7 +15056,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0158</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0159</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0160</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
@@ -15299,7 +15299,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-21-0001</t>
+          <t>FRC-HQ-SLM-C-21-0161</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0162</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0163</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0164</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0165</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0166</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0167</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0168</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0169</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0170</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0171</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0001</t>
+          <t>FRC-HQ-SLM-I-21-0172</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0173</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0174</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0175</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0176</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0177</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
@@ -16697,7 +16697,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0178</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0179</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
@@ -16859,7 +16859,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0180</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0181</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0182</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0183</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0184</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0185</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0186</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0187</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0188</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -17593,7 +17593,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0189</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0190</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0191</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0192</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0193</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0194</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0195</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0196</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-S-21-0001</t>
+          <t>FRC-HQ-SLM-S-21-0197</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -18342,7 +18342,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0001</t>
+          <t>FRC-HQ-SLM-E-21-0198</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0001</t>
+          <t>FRC-HQ-SLM-E-21-0199</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0200</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -18597,7 +18597,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0201</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -18682,7 +18682,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0202</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0203</t>
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
@@ -18852,7 +18852,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0204</t>
         </is>
       </c>
       <c r="F204" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0205</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -19022,7 +19022,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0206</t>
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0207</t>
         </is>
       </c>
       <c r="F207" t="inlineStr"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0208</t>
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0209</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0210</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0211</t>
         </is>
       </c>
       <c r="F211" t="inlineStr"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0212</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0213</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0214</t>
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0215</t>
         </is>
       </c>
       <c r="F215" t="inlineStr"/>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0216</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0217</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0218</t>
         </is>
       </c>
       <c r="F218" t="inlineStr"/>
@@ -20131,7 +20131,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0219</t>
         </is>
       </c>
       <c r="F219" t="inlineStr"/>
@@ -20220,7 +20220,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0220</t>
         </is>
       </c>
       <c r="F220" t="inlineStr"/>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0221</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0222</t>
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
@@ -20471,7 +20471,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0223</t>
         </is>
       </c>
       <c r="F223" t="inlineStr"/>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0224</t>
         </is>
       </c>
       <c r="F224" t="inlineStr"/>
@@ -20637,7 +20637,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0225</t>
         </is>
       </c>
       <c r="F225" t="inlineStr"/>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0226</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0227</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0228</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0229</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -21054,7 +21054,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0230</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -21135,7 +21135,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0231</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -21216,7 +21216,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0232</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -21297,7 +21297,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0233</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0234</t>
         </is>
       </c>
       <c r="F234" t="inlineStr"/>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0235</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
@@ -21544,7 +21544,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-21-0002</t>
+          <t>FRC-HQ-SLM-E-21-0236</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -21629,7 +21629,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-P-21-0002</t>
+          <t>FRC-HQ-SLM-P-21-0237</t>
         </is>
       </c>
       <c r="F237" t="inlineStr"/>
@@ -21710,7 +21710,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-P-21-0002</t>
+          <t>FRC-HQ-SLM-P-21-0238</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-P-21-0002</t>
+          <t>FRC-HQ-SLM-P-21-0239</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-P-21-0002</t>
+          <t>FRC-HQ-SLM-P-21-0240</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-P-21-0002</t>
+          <t>FRC-HQ-SLM-P-21-0241</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -22034,7 +22034,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0242</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -22115,7 +22115,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0243</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -22196,7 +22196,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0244</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -22277,7 +22277,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0245</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0246</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
@@ -22439,7 +22439,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0247</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0248</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0249</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0250</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -22763,7 +22763,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0251</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
@@ -22844,7 +22844,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0252</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
@@ -22925,7 +22925,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0253</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0254</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0255</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -23168,7 +23168,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0256</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -23249,7 +23249,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0257</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
@@ -23330,7 +23330,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0258</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -23411,7 +23411,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0259</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0260</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -23573,7 +23573,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0261</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0262</t>
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
@@ -23735,7 +23735,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0263</t>
         </is>
       </c>
       <c r="F263" t="inlineStr"/>
@@ -23816,7 +23816,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0264</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -23897,7 +23897,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0265</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0266</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0267</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -24140,7 +24140,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0268</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0269</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -24306,7 +24306,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0270</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -24387,7 +24387,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0271</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -24468,7 +24468,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0272</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0273</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-I-21-0002</t>
+          <t>FRC-HQ-SLM-I-21-0274</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
@@ -24711,7 +24711,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0275</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0276</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -24873,7 +24873,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0277</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0278</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -25035,7 +25035,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0279</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -25116,7 +25116,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0280</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -25197,7 +25197,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0281</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0282</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -25359,7 +25359,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0283</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0284</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -25525,7 +25525,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0285</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0286</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0287</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0288</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -25861,7 +25861,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0289</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -25946,7 +25946,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0290</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0291</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
@@ -26116,7 +26116,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0292</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -26201,7 +26201,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0293</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0294</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -26371,7 +26371,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0295</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0296</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -26537,7 +26537,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0297</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -26618,7 +26618,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0298</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0002</t>
+          <t>FRC-HQ-SLM-F-21-0299</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -26780,7 +26780,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0003</t>
+          <t>FRC-HQ-SLM-F-21-0300</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -26861,7 +26861,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0003</t>
+          <t>FRC-HQ-SLM-F-21-0301</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -26942,7 +26942,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-23-0000</t>
+          <t>FRC-HQ-SLM-F-23-0001</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-23-0000</t>
+          <t>FRC-HQ-SLM-F-23-0001</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-23-0000</t>
+          <t>FRC-HQ-SLM-M-23-0002</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-23-0000</t>
+          <t>FRC-HQ-SLM-M-23-0002</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-23-0000</t>
+          <t>FRC-HQ-SLM-M-23-0002</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-M-23-0000</t>
+          <t>FRC-HQ-SLM-M-23-0002</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0000</t>
+          <t>FRC-HQ-SLM-F-21-0003</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -27509,7 +27509,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-21-0000</t>
+          <t>FRC-HQ-SLM-F-21-0003</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-19-0000</t>
+          <t>FRC-HQ-SLM-O-19-0006</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-19-0000</t>
+          <t>FRC-HQ-SLM-O-19-0006</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -27752,7 +27752,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-23-0000</t>
+          <t>FRC-HQ-SLM-F-23-0006</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-F-23-0000</t>
+          <t>FRC-HQ-SLM-F-23-0006</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-23-0000</t>
+          <t>FRC-HQ-SLM-T-23-0006</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -27995,7 +27995,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-23-0000</t>
+          <t>FRC-HQ-SLM-T-23-0006</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -28076,7 +28076,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-23-0000</t>
+          <t>FRC-HQ-SLM-E-23-0006</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-23-0000</t>
+          <t>FRC-HQ-SLM-E-23-0006</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -28238,7 +28238,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-E-23-0000</t>
+          <t>FRC-HQ-SLM-E-23-0006</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -28319,7 +28319,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-22-0000</t>
+          <t>FRC-HQ-SLM-C-22-0006</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-22-0000</t>
+          <t>FRC-HQ-SLM-C-22-0006</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -28481,7 +28481,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -28562,7 +28562,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -28643,7 +28643,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -28805,7 +28805,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -29129,7 +29129,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -29210,7 +29210,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-C-23-0000</t>
+          <t>FRC-HQ-SLM-C-23-0001</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-T-20-0000</t>
+          <t>FRC-HQ-SLM-T-20-0001</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -29534,7 +29534,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>FRC-HQ-SLM-O-21-0000</t>
+          <t>FRC-HQ-SLM-O-21-0001</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
